--- a/data/wfa_window_count_2024-10-21_2026-04-20.xlsx
+++ b/data/wfa_window_count_2024-10-21_2026-04-20.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="6eec91f6-c3ae-4587-83eb-a59bafa" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="7c833f08-3feb-41b0-aabb-ab7a0f7" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
